--- a/gfair_cs/assets/templates/operator-staff.xlsx
+++ b/gfair_cs/assets/templates/operator-staff.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.0.230\ws\__2__기획팀\0. 프로젝트 및 유지보수\2026년\17. 경기도경제과학진흥원_G-FAIR KOREA 구매 및 수출상담 시스템 구축\3. 자료\★공유용_최신버전만 올려주세요\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF2F684-2FA8-4FA3-AA36-DDF6E66053E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D205621-AB25-464F-975F-5462A58ED9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29400" yWindow="3750" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="등록정보" sheetId="1" r:id="rId1"/>
@@ -81,7 +81,41 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Y / N</t>
+    <r>
+      <t>Y / N (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF777777"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">빈칸시 </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF777777"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Y</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF777777"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>자동)</t>
+    </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -89,7 +123,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -143,6 +177,14 @@
       <color rgb="FF777777"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF777777"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
       <charset val="129"/>
     </font>
   </fonts>

--- a/gfair_cs/assets/templates/operator-staff.xlsx
+++ b/gfair_cs/assets/templates/operator-staff.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.0.230\ws\__2__기획팀\0. 프로젝트 및 유지보수\2026년\17. 경기도경제과학진흥원_G-FAIR KOREA 구매 및 수출상담 시스템 구축\3. 자료\★공유용_최신버전만 올려주세요\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D205621-AB25-464F-975F-5462A58ED9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D911C5-9598-4A4F-92BB-C20AAEA99B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29400" yWindow="3750" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30090" yWindow="4440" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="등록정보" sheetId="1" r:id="rId1"/>
@@ -77,45 +77,11 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>사용여부(선택)</t>
+    <t>사용여부(필수)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>Y / N (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF777777"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">빈칸시 </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF777777"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Y</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF777777"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>자동)</t>
-    </r>
+    <t>Y / N</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -123,7 +89,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -177,14 +143,6 @@
       <color rgb="FF777777"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF777777"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
       <charset val="129"/>
     </font>
   </fonts>

--- a/gfair_cs/assets/templates/operator-staff.xlsx
+++ b/gfair_cs/assets/templates/operator-staff.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.0.230\ws\__2__기획팀\0. 프로젝트 및 유지보수\2026년\17. 경기도경제과학진흥원_G-FAIR KOREA 구매 및 수출상담 시스템 구축\3. 자료\★공유용_최신버전만 올려주세요\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hamin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D911C5-9598-4A4F-92BB-C20AAEA99B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE90559E-6135-4C12-8B4A-8FB3E22763D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30090" yWindow="4440" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="등록정보" sheetId="1" r:id="rId1"/>
@@ -146,7 +146,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -163,6 +163,12 @@
         <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -177,7 +183,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -195,7 +201,10 @@
     <xf numFmtId="49" fontId="8" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -420,13 +429,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16.5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
